--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.60243510206932</v>
+        <v>8.547895704086265</v>
       </c>
       <c r="D2" t="n">
-        <v>52.79940704659676</v>
+        <v>8.579903645071973</v>
       </c>
       <c r="E2" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F2" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.83017616791824</v>
+        <v>8.259903627286715</v>
       </c>
       <c r="D3" t="n">
-        <v>52.23516301799804</v>
+        <v>8.488213990424683</v>
       </c>
       <c r="E3" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F3" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.17844900730739</v>
+        <v>6.52899796368745</v>
       </c>
       <c r="D4" t="n">
-        <v>41.59814913897515</v>
+        <v>6.759699235083462</v>
       </c>
       <c r="E4" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F4" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.62822137136963</v>
+        <v>2.702085972847565</v>
       </c>
       <c r="D5" t="n">
-        <v>15.78006855530885</v>
+        <v>2.564261140237687</v>
       </c>
       <c r="E5" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F5" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.9732051785291</v>
+        <v>8.770645841510978</v>
       </c>
       <c r="D6" t="n">
-        <v>52.84863348037708</v>
+        <v>8.587902940561277</v>
       </c>
       <c r="E6" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F6" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.05379400447051</v>
+        <v>9.433741525726459</v>
       </c>
       <c r="D7" t="n">
-        <v>58.31817466079992</v>
+        <v>9.476703382379988</v>
       </c>
       <c r="E7" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F7" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.19151779727748</v>
+        <v>9.94362164205759</v>
       </c>
       <c r="D8" t="n">
-        <v>60.34203033139918</v>
+        <v>9.805579928852367</v>
       </c>
       <c r="E8" t="n">
-        <v>14.06316516216715</v>
+        <v>2.285264338852161</v>
       </c>
       <c r="F8" t="n">
-        <v>14.15102816617824</v>
+        <v>2.299542077003964</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
